--- a/revision_sistematica/extraccion/extraccion_danny_valdiviezo.xlsx
+++ b/revision_sistematica/extraccion/extraccion_danny_valdiviezo.xlsx
@@ -258,7 +258,13 @@
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
-        <t>Cuántos pacientes de este brazo mejoraron, según la definición del propio autor. Si no lo reporta, NA.</t>
+        <t>Pacientes de este brazo que mejoraron según la definición del PROPIO autor.
+   · un número = el artículo lo dice o permite contarlo
+   · 0 = el artículo dice que ninguno mejoró
+   · NA = no lo reporta ni permite deducirlo
+Si el autor no define el éxito pero dice «los tres pacientes se curaron»,
+la cifra SÍ se extrae: pon 3, y escribe SIN DEFINICIÓN OPERATIVA en la
+columna de definición.</t>
       </text>
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
@@ -268,7 +274,19 @@
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
-        <t>En cuántos desapareció la bacteria en cultivo.</t>
+        <t>Pacientes con CULTIVO DE CONTROL NEGATIVO para P. aeruginosa, del mismo
+sitio de infección, DESPUÉS de terminar la fagoterapia. Se toma el primer
+cultivo posterior al fin del tratamiento; anota el día en observaciones.
+Los tres valores NO son intercambiables:
+   · un número = se hizo cultivo y salió negativo en esos pacientes
+   · 0 = se hizo cultivo y SIGUIÓ POSITIVO en todos
+   · NA = no se hizo, o no se reporta, cultivo de control
+FIBROSIS QUÍSTICA Y BRONQUIECTASIAS: un solo cultivo negativo NO cuenta
+como erradicación. En colonización crónica la carga fluctúa y un cultivo
+aislado no demuestra eliminación. Anota NA y explícalo, salvo que el
+artículo declare erradicación sostenida con cultivos seriados.
+Regla completa y por qué:
+quality_reports/decisions/2026-08-11_definicion-erradicacion-y-exito.md</t>
       </text>
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
@@ -293,7 +311,16 @@
     </comment>
     <comment ref="AA1" authorId="0" shapeId="0">
       <text>
-        <t>COPIA la definición del autor, no escribas la tuya. Es lo que después permite ver si todos midieron lo mismo.</t>
+        <t>COPIA la definición del autor. No escribas la tuya.
+Si el artículo NO define qué considera éxito clínico, escribe exactamente:
+        SIN DEFINICIÓN OPERATIVA
+y nada más. NO pegues una frase de la Discusión ni de las Conclusiones.
+Cómo distinguirlas: la definición es una CONDICIÓN («resolución de los
+signos inflamatorios a las 12 semanas»); el resultado es un DESENLACE («el
+paciente evolucionó favorablemente»). Solo la primera va aquí.
+Que la mayoría de los estudios no lo defina ES UN HALLAZGO del manuscrito.
+Si rellenas el hueco con una frase cualquiera, el hueco desaparece del
+registro y con él la prueba de que existía.</t>
       </text>
     </comment>
     <comment ref="AB1" authorId="0" shapeId="0">
@@ -13750,7 +13777,13 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cuántos pacientes de este brazo mejoraron, según la definición del propio autor. Si no lo reporta, NA.</t>
+          <t>Pacientes de este brazo que mejoraron según la definición del PROPIO autor.
+   · un número = el artículo lo dice o permite contarlo
+   · 0 = el artículo dice que ninguno mejoró
+   · NA = no lo reporta ni permite deducirlo
+Si el autor no define el éxito pero dice «los tres pacientes se curaron»,
+la cifra SÍ se extrae: pon 3, y escribe SIN DEFINICIÓN OPERATIVA en la
+columna de definición.</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr"/>
@@ -13776,7 +13809,19 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>En cuántos desapareció la bacteria en cultivo.</t>
+          <t>Pacientes con CULTIVO DE CONTROL NEGATIVO para P. aeruginosa, del mismo
+sitio de infección, DESPUÉS de terminar la fagoterapia. Se toma el primer
+cultivo posterior al fin del tratamiento; anota el día en observaciones.
+Los tres valores NO son intercambiables:
+   · un número = se hizo cultivo y salió negativo en esos pacientes
+   · 0 = se hizo cultivo y SIGUIÓ POSITIVO en todos
+   · NA = no se hizo, o no se reporta, cultivo de control
+FIBROSIS QUÍSTICA Y BRONQUIECTASIAS: un solo cultivo negativo NO cuenta
+como erradicación. En colonización crónica la carga fluctúa y un cultivo
+aislado no demuestra eliminación. Anota NA y explícalo, salvo que el
+artículo declare erradicación sostenida con cultivos seriados.
+Regla completa y por qué:
+quality_reports/decisions/2026-08-11_definicion-erradicacion-y-exito.md</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr"/>
@@ -13841,7 +13886,16 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>COPIA la definición del autor, no escribas la tuya. Es lo que después permite ver si todos midieron lo mismo.</t>
+          <t>COPIA la definición del autor. No escribas la tuya.
+Si el artículo NO define qué considera éxito clínico, escribe exactamente:
+        SIN DEFINICIÓN OPERATIVA
+y nada más. NO pegues una frase de la Discusión ni de las Conclusiones.
+Cómo distinguirlas: la definición es una CONDICIÓN («resolución de los
+signos inflamatorios a las 12 semanas»); el resultado es un DESENLACE («el
+paciente evolucionó favorablemente»). Solo la primera va aquí.
+Que la mayoría de los estudios no lo defina ES UN HALLAZGO del manuscrito.
+Si rellenas el hueco con una frase cualquiera, el hueco desaparece del
+registro y con él la prueba de que existía.</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr"/>
